--- a/roadline-geojson/深川出張所管内座標成果.xlsx
+++ b/roadline-geojson/深川出張所管内座標成果.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365tsukuba-my.sharepoint.com/personal/s1911313_u_tsukuba_ac_jp/Documents/GitHub/roadline-geojson/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="8_{F53FA4F9-F07A-6547-839F-49342C10458D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA116BDF-F8A6-524F-8E43-86B448EF4784}"/>
+  <xr:revisionPtr revIDLastSave="285" documentId="8_{F53FA4F9-F07A-6547-839F-49342C10458D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E93A536E-63F5-E449-BC0F-87DCCD4612E3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="5" xr2:uid="{F04191A0-DEB6-7045-9808-29928ABCA6F7}"/>
+    <workbookView xWindow="-20" yWindow="780" windowWidth="29400" windowHeight="16660" activeTab="1" xr2:uid="{F04191A0-DEB6-7045-9808-29928ABCA6F7}"/>
   </bookViews>
   <sheets>
     <sheet name="1047 深川雨竜線" sheetId="1" r:id="rId1"/>
-    <sheet name="3280 妹背牛停車場線" sheetId="3" r:id="rId2"/>
-    <sheet name="3284 深川停車場線" sheetId="5" r:id="rId3"/>
-    <sheet name="3324 石狩沼田停車場線" sheetId="6" r:id="rId4"/>
-    <sheet name="3372 秩父別停車場線" sheetId="7" r:id="rId5"/>
-    <sheet name="3429 多度志停車場線" sheetId="8" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId7"/>
+    <sheet name="1139 江別奈井江線" sheetId="9" r:id="rId2"/>
+    <sheet name="3280 妹背牛停車場線" sheetId="3" r:id="rId3"/>
+    <sheet name="3284 深川停車場線" sheetId="5" r:id="rId4"/>
+    <sheet name="3324 石狩沼田停車場線" sheetId="6" r:id="rId5"/>
+    <sheet name="3372 秩父別停車場線" sheetId="7" r:id="rId6"/>
+    <sheet name="3429 多度志停車場線" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="227">
   <si>
     <t>R-14</t>
   </si>
@@ -692,120 +693,6 @@
       <t>ジョガイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HL-13</t>
-  </si>
-  <si>
-    <t>HL-12</t>
-  </si>
-  <si>
-    <t>HL-11</t>
-  </si>
-  <si>
-    <t>HL-7慶</t>
-  </si>
-  <si>
-    <t>H元R-8蜜</t>
-  </si>
-  <si>
-    <t>HL-5</t>
-  </si>
-  <si>
-    <t>HR-6変</t>
-  </si>
-  <si>
-    <t>HR-4賞</t>
-  </si>
-  <si>
-    <t>HL-2</t>
-  </si>
-  <si>
-    <t>H元L-1寶</t>
-  </si>
-  <si>
-    <t>H元R-1</t>
-  </si>
-  <si>
-    <t>H元R-19慶</t>
-  </si>
-  <si>
-    <t>HER-18*</t>
-  </si>
-  <si>
-    <t>HotL-16*</t>
-  </si>
-  <si>
-    <t>HER-173</t>
-  </si>
-  <si>
-    <t>HテルL-15</t>
-  </si>
-  <si>
-    <t>元R-16</t>
-  </si>
-  <si>
-    <t>btL-14*</t>
-  </si>
-  <si>
-    <t>HR-15慶</t>
-  </si>
-  <si>
-    <t>H元R-14</t>
-  </si>
-  <si>
-    <t>元R-13</t>
-  </si>
-  <si>
-    <t>HTR-12Z</t>
-  </si>
-  <si>
-    <t>HtL-10</t>
-  </si>
-  <si>
-    <t>HER-11A</t>
-  </si>
-  <si>
-    <t>HtL-9*</t>
-  </si>
-  <si>
-    <t>H元R-10麥</t>
-  </si>
-  <si>
-    <t>HEL-8&amp;</t>
-  </si>
-  <si>
-    <t>H元R-9</t>
-  </si>
-  <si>
-    <t>H元L-6蜜</t>
-  </si>
-  <si>
-    <t>H元R-7</t>
-  </si>
-  <si>
-    <t>HũL-4&amp;</t>
-  </si>
-  <si>
-    <t>HER-5#</t>
-  </si>
-  <si>
-    <t>tL-3*</t>
-  </si>
-  <si>
-    <t>H元R-3</t>
-  </si>
-  <si>
-    <t>H元R-2</t>
-  </si>
-  <si>
-    <t>S63R-72</t>
-  </si>
-  <si>
-    <t>S63R-5#</t>
-  </si>
-  <si>
-    <t>S63R-6#</t>
   </si>
   <si>
     <t>L-1座標欠損</t>
@@ -866,6 +753,178 @@
     <rPh sb="9" eb="11">
       <t>ジョガイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>幅員欠損</t>
+    <rPh sb="0" eb="2">
+      <t>フクイn</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッソn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>L8</t>
+  </si>
+  <si>
+    <t>L-1(51-2)座標欠損</t>
+    <rPh sb="9" eb="13">
+      <t>ザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>//</t>
+  </si>
+  <si>
+    <t>51-3</t>
+  </si>
+  <si>
+    <t>51-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>L-I1</t>
+  </si>
+  <si>
+    <t>51-4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HI4 R3</t>
+  </si>
+  <si>
+    <t>-56.788.477</t>
+  </si>
+  <si>
+    <t>HI4 L4</t>
+  </si>
+  <si>
+    <t>// R4</t>
+  </si>
+  <si>
+    <t>I/ R5</t>
+  </si>
+  <si>
+    <t>|/ R6</t>
+  </si>
+  <si>
+    <t>|/ L7</t>
+  </si>
+  <si>
+    <t>// R7</t>
+  </si>
+  <si>
+    <t>// R8</t>
+  </si>
+  <si>
+    <t>|/ L9</t>
+  </si>
+  <si>
+    <t>|/ R9</t>
+  </si>
+  <si>
+    <t>I LIO</t>
+  </si>
+  <si>
+    <t>I RIO</t>
+  </si>
+  <si>
+    <t>/ LI!</t>
+  </si>
+  <si>
+    <t>/ RII</t>
+  </si>
+  <si>
+    <t>// LI2</t>
+  </si>
+  <si>
+    <t>1I R12</t>
+  </si>
+  <si>
+    <t>|/ LI3</t>
+  </si>
+  <si>
+    <t>| R13</t>
+  </si>
+  <si>
+    <t>L14</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>LI5</t>
+  </si>
+  <si>
+    <t>|/ RI5</t>
+  </si>
+  <si>
+    <t>|/ LI6</t>
+  </si>
+  <si>
+    <t>I RI6</t>
+  </si>
+  <si>
+    <t>L17</t>
+  </si>
+  <si>
+    <t>|/ R17</t>
+  </si>
+  <si>
+    <t>L18</t>
+  </si>
+  <si>
+    <t>|/ RI8</t>
+  </si>
+  <si>
+    <t>L19</t>
+  </si>
+  <si>
+    <t>|/ RI9</t>
+  </si>
+  <si>
+    <t>L20</t>
+  </si>
+  <si>
+    <t>|/ R20</t>
+  </si>
+  <si>
+    <t>L21</t>
+  </si>
+  <si>
+    <t>|/ R21</t>
+  </si>
+  <si>
+    <t>L22</t>
+  </si>
+  <si>
+    <t>HI4 R22</t>
+  </si>
+  <si>
+    <t>L23</t>
+  </si>
+  <si>
+    <t>L24</t>
+  </si>
+  <si>
+    <t>H.I4 L25</t>
+  </si>
+  <si>
+    <t>51-5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -929,7 +988,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9116,6 +9175,2285 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470408CE-177A-B04F-8F13-970A2A8F62E4}">
+  <dimension ref="A1:L105"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="3.33203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="3">
+        <v>-96369.502999999997</v>
+      </c>
+      <c r="D2" s="3">
+        <v>-57431.845000000001</v>
+      </c>
+      <c r="E2" s="3">
+        <v>34.25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="3">
+        <v>-96377.752999999997</v>
+      </c>
+      <c r="J2" s="3">
+        <v>-57367.535000000003</v>
+      </c>
+      <c r="K2" s="3">
+        <v>30.45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="3">
+        <v>-96367.442999999999</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-57412.355000000003</v>
+      </c>
+      <c r="E3" s="3">
+        <v>15.51</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="3">
+        <v>-96365.342999999993</v>
+      </c>
+      <c r="J3" s="3">
+        <v>-57374.455000000002</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="3">
+        <v>-96318.543000000005</v>
+      </c>
+      <c r="J5" s="3">
+        <v>-57368.154999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="3">
+        <v>-96275.444000000003</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-57391.355000000003</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3">
+        <v>-96263.644</v>
+      </c>
+      <c r="J6" s="3">
+        <v>-57363.355000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3">
+        <v>-96252.944000000003</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-57384.754999999997</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="3">
+        <v>-96257.02</v>
+      </c>
+      <c r="J7" s="3">
+        <v>-57362.322999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-96212.194000000003</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-57376.353999999999</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
+        <v>-96226.282999999996</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-57356.284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-96178.444000000003</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-57370.103999999999</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-96175.705000000002</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-57345.785000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-96172.644</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-57373.983999999997</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-96174.914000000004</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-57344.864000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-96172.447</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-57375.391000000003</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="3">
+        <v>-96158.724000000002</v>
+      </c>
+      <c r="J11" s="3">
+        <v>-57342.523999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-96145.455000000002</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-57371.569000000003</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="3">
+        <v>-96149.433999999994</v>
+      </c>
+      <c r="J12" s="3">
+        <v>-57343.343999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-96146.323999999993</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-57365.453999999998</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="3">
+        <v>-96138.752999999997</v>
+      </c>
+      <c r="J13" s="3">
+        <v>-57341.076000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-96135.584000000003</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-57363.444000000003</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-96138.877999999997</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-57340.182000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-96112.683999999994</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-57359.163999999997</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-96127.120999999999</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-57337.106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-96112.459000000003</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-57360.766000000003</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="3">
+        <v>-96084.895000000004</v>
+      </c>
+      <c r="J16" s="3">
+        <v>-57328.983</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-96095.581000000006</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-57358.008000000002</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-96068.414999999994</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-57326.144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-96042.286999999997</v>
+      </c>
+      <c r="D18" s="3">
+        <v>-57346.55</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-95990.365000000005</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-57310.502999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-96042.345000000001</v>
+      </c>
+      <c r="D19" s="3">
+        <v>-57346.023999999998</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="3">
+        <v>-95962.695000000007</v>
+      </c>
+      <c r="J19" s="3">
+        <v>-57302.313000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3">
+        <v>-96027.294999999998</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-57343.214</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-95939.955000000002</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-57290.623</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-95955.794999999998</v>
+      </c>
+      <c r="D21" s="3">
+        <v>-57329.843000000001</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-95920.785000000003</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-57272.743000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-95920.744999999995</v>
+      </c>
+      <c r="D22" s="3">
+        <v>-57312.192999999999</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="3">
+        <v>-95908.595000000001</v>
+      </c>
+      <c r="J22" s="3">
+        <v>-57249.252999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-95905.764999999999</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-57293.012999999999</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-95902.335000000006</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-57227.383000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3">
+        <v>-95895.986000000004</v>
+      </c>
+      <c r="D24" s="3">
+        <v>-57279.652999999998</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-95897.675000000003</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-57190.883000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-95889.576000000001</v>
+      </c>
+      <c r="D25" s="3">
+        <v>-57269.332999999999</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="3">
+        <v>-95893.895000000004</v>
+      </c>
+      <c r="J25" s="3">
+        <v>-57191.262999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-95884.895999999993</v>
+      </c>
+      <c r="D26" s="3">
+        <v>-57256.423000000003</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-95888.865000000005</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-57141.514000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-95880.106</v>
+      </c>
+      <c r="D27" s="3">
+        <v>-57236.593000000001</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-95883.835000000006</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-57091.773999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-95877.725999999995</v>
+      </c>
+      <c r="D28" s="3">
+        <v>-57223.673000000003</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-95878.815000000002</v>
+      </c>
+      <c r="J28" s="3">
+        <v>-57042.023999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-95876.406000000003</v>
+      </c>
+      <c r="D29" s="3">
+        <v>-57210.832999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-95875.805999999997</v>
+      </c>
+      <c r="D30" s="3">
+        <v>-57193.093000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="3">
+        <v>-95870.785999999993</v>
+      </c>
+      <c r="D31" s="3">
+        <v>-57143.343000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="3">
+        <v>-95865.766000000003</v>
+      </c>
+      <c r="D32" s="3">
+        <v>-57093.603999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="3">
+        <v>-95860.736000000004</v>
+      </c>
+      <c r="D33" s="3">
+        <v>-57043.853999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="3">
+        <v>-95855.714999999997</v>
+      </c>
+      <c r="D35" s="3">
+        <v>-56994.103999999999</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-95873.794999999998</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-56992.273999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="3">
+        <v>-95850.695000000007</v>
+      </c>
+      <c r="D36" s="3">
+        <v>-56944.353999999999</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="3">
+        <v>-95871.285000000003</v>
+      </c>
+      <c r="J36" s="3">
+        <v>-56967.413999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="3">
+        <v>-95845.675000000003</v>
+      </c>
+      <c r="D37" s="3">
+        <v>-56894.603999999999</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="3">
+        <v>-95874.264999999999</v>
+      </c>
+      <c r="J37" s="3">
+        <v>-56967.114000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="3">
+        <v>-95840.654999999999</v>
+      </c>
+      <c r="D38" s="3">
+        <v>-56844.864000000001</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" s="3">
+        <v>-95866.755000000005</v>
+      </c>
+      <c r="J38" s="3">
+        <v>-56892.694000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="3">
+        <v>-95835.625</v>
+      </c>
+      <c r="D39" s="3">
+        <v>-56795.114000000001</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="3">
+        <v>-95861.735000000001</v>
+      </c>
+      <c r="J39" s="3">
+        <v>-56842.944000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="3">
+        <v>-95830.604999999996</v>
+      </c>
+      <c r="D40" s="3">
+        <v>-56745.364999999998</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I40" s="3">
+        <v>-95856.714999999997</v>
+      </c>
+      <c r="J40" s="3">
+        <v>-56793.194000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="3">
+        <v>-95826.138000000006</v>
+      </c>
+      <c r="D41" s="3">
+        <v>-56701.341</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" s="3">
+        <v>-95851.695000000007</v>
+      </c>
+      <c r="J41" s="3">
+        <v>-56743.455000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="3">
+        <v>-95825.392999999996</v>
+      </c>
+      <c r="D42" s="3">
+        <v>-56698.887000000002</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I42" s="3">
+        <v>-95846.956999999995</v>
+      </c>
+      <c r="J42" s="3">
+        <v>-56696.696000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="3">
+        <v>-95820.804999999993</v>
+      </c>
+      <c r="D43" s="3">
+        <v>-56667.737000000001</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
+        <v>-95844.239000000001</v>
+      </c>
+      <c r="J43" s="3">
+        <v>-56651.94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3">
+        <v>-95822.732999999993</v>
+      </c>
+      <c r="D44" s="3">
+        <v>-56667.618000000002</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
+        <v>-95848.082999999999</v>
+      </c>
+      <c r="J44" s="3">
+        <v>-56651.553</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="3">
+        <v>-95821.565000000002</v>
+      </c>
+      <c r="D45" s="3">
+        <v>-56656.035000000003</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
+        <v>-95845.781000000003</v>
+      </c>
+      <c r="J45" s="3">
+        <v>-56628.749000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="3">
+        <v>-95815.365999999995</v>
+      </c>
+      <c r="D46" s="3">
+        <v>-56650.974999999999</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="3">
+        <v>-95841.971000000005</v>
+      </c>
+      <c r="J46" s="3">
+        <v>-56629.133999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="3">
+        <v>-95799.748999999996</v>
+      </c>
+      <c r="D47" s="3">
+        <v>-56652.546000000002</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="3">
+        <v>-95841.41</v>
+      </c>
+      <c r="J47" s="3">
+        <v>-56623.553</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="3">
+        <v>-95799.87</v>
+      </c>
+      <c r="D48" s="3">
+        <v>-56653.387999999999</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>-95815.495999999999</v>
+      </c>
+      <c r="J48" s="3">
+        <v>-56626.186000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="3">
+        <v>-95750.01</v>
+      </c>
+      <c r="D49" s="3">
+        <v>-56658.258000000002</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" s="3">
+        <v>-95813.020999999993</v>
+      </c>
+      <c r="J49" s="3">
+        <v>-56628.866000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="3">
+        <v>-95713.152000000002</v>
+      </c>
+      <c r="D50" s="3">
+        <v>-56661.540999999997</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I50" s="3">
+        <v>-95801.929000000004</v>
+      </c>
+      <c r="J50" s="3">
+        <v>-56630.004999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="3">
+        <v>-95712.627999999997</v>
+      </c>
+      <c r="D51" s="3">
+        <v>-56661.341999999997</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I51" s="3">
+        <v>-95787.553</v>
+      </c>
+      <c r="J51" s="3">
+        <v>-56632.286</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="3">
+        <v>-95665.555999999997</v>
+      </c>
+      <c r="D52" s="3">
+        <v>-56666.093999999997</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I52" s="3">
+        <v>-95747.823000000004</v>
+      </c>
+      <c r="J52" s="3">
+        <v>-56636.97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="3">
+        <v>-95615.807000000001</v>
+      </c>
+      <c r="D53" s="3">
+        <v>-56671.114000000001</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I53" s="3">
+        <v>-95711.269</v>
+      </c>
+      <c r="J53" s="3">
+        <v>-56643.205000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="3">
+        <v>-95566.066999999995</v>
+      </c>
+      <c r="D54" s="3">
+        <v>-56676.133999999998</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I54" s="3">
+        <v>-95680.986000000004</v>
+      </c>
+      <c r="J54" s="3">
+        <v>-56646.254000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="3">
+        <v>-95516.316999999995</v>
+      </c>
+      <c r="D55" s="3">
+        <v>-56681.163</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I55" s="3">
+        <v>-95621.286999999997</v>
+      </c>
+      <c r="J55" s="3">
+        <v>-56652.284</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="3">
+        <v>-95466.567999999999</v>
+      </c>
+      <c r="D57" s="3">
+        <v>-56686.182999999997</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" s="3">
+        <v>-95451.157999999996</v>
+      </c>
+      <c r="J57" s="3">
+        <v>-56669.453000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="3">
+        <v>-95416.817999999999</v>
+      </c>
+      <c r="D58" s="3">
+        <v>-56691.203000000001</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" s="3">
+        <v>-95264.599000000002</v>
+      </c>
+      <c r="J58" s="3">
+        <v>-56688.292000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="3">
+        <v>-95377.028000000006</v>
+      </c>
+      <c r="D59" s="3">
+        <v>-56695.222999999998</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="3">
+        <v>-95226.036999999997</v>
+      </c>
+      <c r="J59" s="3">
+        <v>-56692.184000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="3">
+        <v>-95327.278000000006</v>
+      </c>
+      <c r="D60" s="3">
+        <v>-56700.243000000002</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="3">
+        <v>-95167.29</v>
+      </c>
+      <c r="J60" s="3">
+        <v>-56697.205000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="3">
+        <v>-95277.528999999995</v>
+      </c>
+      <c r="D61" s="3">
+        <v>-56705.262000000002</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="3">
+        <v>-95126.543000000005</v>
+      </c>
+      <c r="J61" s="3">
+        <v>-56702.226999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="3">
+        <v>-95227.862999999998</v>
+      </c>
+      <c r="D62" s="3">
+        <v>-56710.271999999997</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
+        <v>-95076.796000000002</v>
+      </c>
+      <c r="J62" s="3">
+        <v>-56707.249000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="3">
+        <v>-95178.115999999995</v>
+      </c>
+      <c r="D63" s="3">
+        <v>-56715.294000000002</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I63" s="3">
+        <v>-95027.048999999999</v>
+      </c>
+      <c r="J63" s="3">
+        <v>-56712.271000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="3">
+        <v>-95128.369000000006</v>
+      </c>
+      <c r="D64" s="3">
+        <v>-56720.315999999999</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I64" s="3">
+        <v>-94977.301999999996</v>
+      </c>
+      <c r="J64" s="3">
+        <v>-56717.292999999998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="3">
+        <v>-95078.622000000003</v>
+      </c>
+      <c r="D65" s="3">
+        <v>-56725.338000000003</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I65" s="3">
+        <v>-94925.565000000002</v>
+      </c>
+      <c r="J65" s="3">
+        <v>-56722.516000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="3">
+        <v>-95028.875</v>
+      </c>
+      <c r="D66" s="3">
+        <v>-56730.36</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
+        <v>-94877.808000000005</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-56727.336000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C67" s="3">
+        <v>-94979.127999999997</v>
+      </c>
+      <c r="D67" s="3">
+        <v>-56735.381999999998</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I67" s="3">
+        <v>-94828.061000000002</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-56732.358</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="3">
+        <v>-94929.380999999994</v>
+      </c>
+      <c r="D68" s="3">
+        <v>-56740.404000000002</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I68" s="3">
+        <v>-94778.313999999998</v>
+      </c>
+      <c r="J68" s="3">
+        <v>-56737.38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="3">
+        <v>-94879.634000000005</v>
+      </c>
+      <c r="D69" s="3">
+        <v>-56745.425999999999</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3">
+        <v>-94733.17</v>
+      </c>
+      <c r="J69" s="3">
+        <v>-56741.936999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="3">
+        <v>-94829.887000000002</v>
+      </c>
+      <c r="D70" s="3">
+        <v>-56750.447999999997</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>-94713.646999999997</v>
+      </c>
+      <c r="J70" s="3">
+        <v>-56737.877</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="3">
+        <v>-94780.14</v>
+      </c>
+      <c r="D71" s="3">
+        <v>-56755.47</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I71" s="3">
+        <v>-94695.301999999996</v>
+      </c>
+      <c r="J71" s="3">
+        <v>-56737.218999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="3">
+        <v>-94732.402000000002</v>
+      </c>
+      <c r="D72" s="3">
+        <v>-56760.288999999997</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-94655.191999999995</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-56739.428999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="3">
+        <v>-94732.521999999997</v>
+      </c>
+      <c r="D73" s="3">
+        <v>-56761.468999999997</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I73" s="3">
+        <v>-94656.88</v>
+      </c>
+      <c r="J73" s="3">
+        <v>-56749.637999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="3">
+        <v>-94716.312000000005</v>
+      </c>
+      <c r="D74" s="3">
+        <v>-56763.669000000002</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I74" s="3">
+        <v>-94650.96</v>
+      </c>
+      <c r="J74" s="3">
+        <v>-56750.235999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="3">
+        <v>-94716.13</v>
+      </c>
+      <c r="D75" s="3">
+        <v>-56761.93</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I75" s="3">
+        <v>-94646.274999999994</v>
+      </c>
+      <c r="J75" s="3">
+        <v>-56756.927000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" s="3">
+        <v>-94656.606</v>
+      </c>
+      <c r="D76" s="3">
+        <v>-56767.938000000002</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-94600.922000000006</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-56761.557999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="3">
+        <v>-94650.824999999997</v>
+      </c>
+      <c r="D77" s="3">
+        <v>-56767.548000000003</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" s="3">
+        <v>-94599.138000000006</v>
+      </c>
+      <c r="J77" s="3">
+        <v>-56754.457999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" s="3">
+        <v>-94647.062999999995</v>
+      </c>
+      <c r="D78" s="3">
+        <v>-56764.624000000003</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I78" s="3">
+        <v>-94586.551000000007</v>
+      </c>
+      <c r="J78" s="3">
+        <v>-56756.737000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="3">
+        <v>-94595.603000000003</v>
+      </c>
+      <c r="D79" s="3">
+        <v>-56769.862000000001</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I79" s="3">
+        <v>-94510.99</v>
+      </c>
+      <c r="J79" s="3">
+        <v>-56764.364000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="3">
+        <v>-94590.837</v>
+      </c>
+      <c r="D80" s="3">
+        <v>-56777.631999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="3">
+        <v>-94551.062999999995</v>
+      </c>
+      <c r="D81" s="3">
+        <v>-56782.408000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" s="3">
+        <v>-94516.362999999998</v>
+      </c>
+      <c r="D82" s="3">
+        <v>-56782.097999999998</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" s="3">
+        <v>-94453.126999999993</v>
+      </c>
+      <c r="D84" s="3">
+        <v>-56788.476999999999</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84" s="3">
+        <v>-94450.796000000002</v>
+      </c>
+      <c r="J84" s="3">
+        <v>-56770.44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85" s="3">
+        <v>-94403.38</v>
+      </c>
+      <c r="D85" s="3">
+        <v>-56793.498</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" s="3">
+        <v>-94401.546000000002</v>
+      </c>
+      <c r="J85" s="3">
+        <v>-56775.411</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" s="3">
+        <v>-94353.633000000002</v>
+      </c>
+      <c r="D86" s="3">
+        <v>-56798.52</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I86" s="3">
+        <v>-94351.798999999999</v>
+      </c>
+      <c r="J86" s="3">
+        <v>-56780.432999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" s="3">
+        <v>-94303.885999999999</v>
+      </c>
+      <c r="D87" s="3">
+        <v>-56803.540999999997</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I87" s="3">
+        <v>-94302.051999999996</v>
+      </c>
+      <c r="J87" s="3">
+        <v>-56785.453999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="3">
+        <v>-94254.138000000006</v>
+      </c>
+      <c r="D88" s="3">
+        <v>-56808.563000000002</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I88" s="3">
+        <v>-94252.304000000004</v>
+      </c>
+      <c r="J88" s="3">
+        <v>-56790.476000000002</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="3">
+        <v>-94204.391000000003</v>
+      </c>
+      <c r="D89" s="3">
+        <v>-56813.584000000003</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-94202.557000000001</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-56795.497000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="3">
+        <v>-94154.644</v>
+      </c>
+      <c r="D90" s="3">
+        <v>-56818.606</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I90" s="3">
+        <v>-94152.81</v>
+      </c>
+      <c r="J90" s="3">
+        <v>-56800.519</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="3">
+        <v>-94136.555999999997</v>
+      </c>
+      <c r="D91" s="3">
+        <v>-56820.432000000001</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-94134.721999999994</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-56802.343999999997</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" s="3">
+        <v>-94086.808999999994</v>
+      </c>
+      <c r="D92" s="3">
+        <v>-56825.453000000001</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I92" s="3">
+        <v>-94084.975000000006</v>
+      </c>
+      <c r="J92" s="3">
+        <v>-56807.364999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="3">
+        <v>-94037.062000000005</v>
+      </c>
+      <c r="D93" s="3">
+        <v>-56830.474999999999</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I93" s="3">
+        <v>-94035.228000000003</v>
+      </c>
+      <c r="J93" s="3">
+        <v>-56812.387000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="3">
+        <v>-93987.313999999998</v>
+      </c>
+      <c r="D94" s="3">
+        <v>-56835.495999999999</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-93985.48</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-56817.408000000003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="3">
+        <v>-93949.804999999993</v>
+      </c>
+      <c r="D95" s="3">
+        <v>-56839.283000000003</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I95" s="3">
+        <v>-93935.732999999993</v>
+      </c>
+      <c r="J95" s="3">
+        <v>-56822.43</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="3">
+        <v>-93887.82</v>
+      </c>
+      <c r="D96" s="3">
+        <v>-56845.538999999997</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-93885.986000000004</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-56827.451000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" s="3">
+        <v>-93838.073000000004</v>
+      </c>
+      <c r="D97" s="3">
+        <v>-56850.559999999998</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3">
+        <v>-93836.239000000001</v>
+      </c>
+      <c r="J97" s="3">
+        <v>-56832.472999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" s="3">
+        <v>-93803.648000000001</v>
+      </c>
+      <c r="D98" s="3">
+        <v>-56854.035000000003</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I98" s="3">
+        <v>-93786.491999999998</v>
+      </c>
+      <c r="J98" s="3">
+        <v>-56837.493999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" s="3">
+        <v>-93744.846999999994</v>
+      </c>
+      <c r="D99" s="3">
+        <v>-56859.970999999998</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I99" s="3">
+        <v>-93736.744000000006</v>
+      </c>
+      <c r="J99" s="3">
+        <v>-56842.516000000003</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" s="3">
+        <v>-93689.726999999999</v>
+      </c>
+      <c r="D100" s="3">
+        <v>-56865.534</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-93688.986999999994</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-56847.336000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C101" s="3">
+        <v>-93643.063999999998</v>
+      </c>
+      <c r="D101" s="3">
+        <v>-56870.243999999999</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-93641.23</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-56852.156999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C102" s="3">
+        <v>-93593.154999999999</v>
+      </c>
+      <c r="D102" s="3">
+        <v>-56875.281999999999</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-93591.316000000006</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-56857.195</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C103" s="3">
+        <v>-93575.066999999995</v>
+      </c>
+      <c r="D103" s="3">
+        <v>-56877.107000000004</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I103" s="3">
+        <v>-93586.289000000004</v>
+      </c>
+      <c r="J103" s="3">
+        <v>-56807.447999999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104" s="3">
+        <v>-93573.228000000003</v>
+      </c>
+      <c r="D104" s="3">
+        <v>-56859.021000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C105" s="3">
+        <v>-93568.201000000001</v>
+      </c>
+      <c r="D105" s="3">
+        <v>-56809.273999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E19689-4033-3144-BCF0-96475A887E99}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
@@ -9558,7 +11896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44109EA9-AB10-884D-8D5F-F5949E94017B}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
@@ -9927,7 +12265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE4D1B1-1CE2-1444-ABC3-4BEB11327558}">
   <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
@@ -10310,7 +12648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EC53A2-8AF1-2142-97BA-41848EB95819}">
   <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
@@ -10969,7 +13307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEF0E46-3DF1-F14B-9946-8B856050B41C}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
@@ -11046,7 +13384,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -11096,7 +13434,7 @@
         <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -11186,7 +13524,7 @@
         <v>8</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -11235,7 +13573,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -11455,7 +13793,7 @@
         <v>-17762.026000000002</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>63</v>
@@ -11545,7 +13883,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>66</v>
@@ -11560,7 +13898,7 @@
         <v>8</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -11582,7 +13920,7 @@
         <v>-17834.898000000001</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -11599,7 +13937,7 @@
         <v>-17844.898000000001</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -11609,9 +13947,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6739C2D0-D42D-6D40-A277-2562649103E3}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -11623,553 +13961,1017 @@
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:14" ht="19" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5">
+        <v>-94450.796000000002</v>
+      </c>
+      <c r="C1" s="5">
+        <v>-56770.44</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>186</v>
+      </c>
       <c r="E1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="F1" s="5">
+        <v>-94453.126999999993</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1">
+        <f>IF(ISERROR(VALUE("-94"&amp;B1)), B1,VALUE("-94"&amp;B1))</f>
+        <v>-94450.796000000002</v>
+      </c>
+      <c r="J1">
+        <f>IF(ISERROR(VALUE("-56"&amp;C1)), C1,VALUE("-56"&amp;C1))</f>
+        <v>-56770.44</v>
+      </c>
+      <c r="M1">
+        <f>IF(ISERROR(VALUE("-94"&amp;F1)), F1,VALUE("-94"&amp;F1))</f>
+        <v>-94453.126999999993</v>
+      </c>
+      <c r="N1" t="str">
+        <f>IF(ISERROR(VALUE("-56"&amp;G1)), G1,VALUE("-56"&amp;G1))</f>
+        <v>-56.788.477</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="B2" s="4">
+        <v>-94401.546000000002</v>
+      </c>
+      <c r="C2" s="4">
+        <v>-56775.411</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>189</v>
+      </c>
       <c r="E2" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F2" s="4">
-        <v>-20610.807000000001</v>
+        <v>-94403.38</v>
       </c>
       <c r="G2" s="4">
-        <v>-17519.03</v>
+        <v>-56793.498</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>181</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:I22" si="0">IF(ISERROR(VALUE("-94"&amp;B2)), B2,VALUE("-94"&amp;B2))</f>
+        <v>-94401.546000000002</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:J22" si="1">IF(ISERROR(VALUE("-56"&amp;C2)), C2,VALUE("-56"&amp;C2))</f>
+        <v>-56775.411</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:M22" si="2">IF(ISERROR(VALUE("-94"&amp;F2)), F2,VALUE("-94"&amp;F2))</f>
+        <v>-94403.38</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N25" si="3">IF(ISERROR(VALUE("-56"&amp;G2)), G2,VALUE("-56"&amp;G2))</f>
+        <v>-56793.498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="4">
+        <v>-94351.798999999999</v>
+      </c>
+      <c r="C3" s="4">
+        <v>-56780.432999999997</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="4">
-        <v>-20659.037</v>
+        <v>-94353.633000000002</v>
       </c>
       <c r="G3" s="4">
-        <v>-17533.371999999999</v>
+        <v>-56798.52</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>178</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>-94351.798999999999</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="1"/>
+        <v>-56780.432999999997</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="2"/>
+        <v>-94353.633000000002</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="3"/>
+        <v>-56798.52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4">
-        <v>-20604.226999999999</v>
+        <v>-94302.051999999996</v>
       </c>
       <c r="C4" s="4">
-        <v>-17533.760999999999</v>
+        <v>-56785.453999999998</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>-20697.377</v>
+        <v>-94303.885999999999</v>
       </c>
       <c r="G4" s="4">
-        <v>-17544.773000000001</v>
+        <v>-56803.540999999997</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>192</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>-94302.051999999996</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>-56785.453999999998</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>-94303.885999999999</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="3"/>
+        <v>-56803.540999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="4">
-        <v>-20654.475999999999</v>
+        <v>-94252.304000000004</v>
       </c>
       <c r="C5" s="4">
-        <v>-17548.702000000001</v>
+        <v>-56790.476000000002</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4">
-        <v>-20774.065999999999</v>
+        <v>-94254.138000000006</v>
       </c>
       <c r="G5" s="4">
-        <v>-17567.575000000001</v>
+        <v>-56808.563000000002</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>179</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>-94252.304000000004</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>-56790.476000000002</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>-94254.138000000006</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>-56808.563000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4">
-        <v>-20692.815999999999</v>
+        <v>-94202.557000000001</v>
       </c>
       <c r="C6" s="4">
-        <v>-17560.102999999999</v>
+        <v>-56795.497000000003</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="4">
-        <v>-20820.745999999999</v>
+        <v>-94204.391000000003</v>
       </c>
       <c r="G6" s="4">
-        <v>-17581.455999999998</v>
+        <v>-56813.584000000003</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>195</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>-94202.557000000001</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>-56795.497000000003</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>-94204.391000000003</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>-56813.584000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>-20731.166000000001</v>
+        <v>-94152.81</v>
       </c>
       <c r="C7" s="4">
-        <v>-17571.504000000001</v>
+        <v>-56800.519</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="4">
-        <v>-20825.065999999999</v>
+        <v>-94154.644</v>
       </c>
       <c r="G7" s="4">
-        <v>-17578.036</v>
+        <v>-56818.606</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>197</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>-94152.81</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>-56800.519</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>-94154.644</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>-56818.606</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>-21469.526999999998</v>
+        <v>-94134.721999999994</v>
       </c>
       <c r="C8" s="4">
-        <v>-17582.912</v>
+        <v>-56802.343999999997</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="4">
-        <v>-20832.045999999998</v>
+        <v>-94136.555999999997</v>
       </c>
       <c r="G8" s="4">
-        <v>-17580.106</v>
+        <v>-56820.432000000001</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>199</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>-94134.721999999994</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>-56802.343999999997</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>-94136.555999999997</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>-56820.432000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="4">
-        <v>-20807.845000000001</v>
+        <v>-9484.9750000000004</v>
       </c>
       <c r="C9" s="4">
-        <v>-17594.306</v>
+        <v>-56807.364999999998</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="4">
-        <v>-20830.876</v>
+        <v>-9486.8089999999993</v>
       </c>
       <c r="G9" s="4">
-        <v>-17584.466</v>
+        <v>-56825.453000000001</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>201</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>-9484.9750000000004</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>-56807.364999999998</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>-9486.8089999999993</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>-56825.453000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="4">
-        <v>-20843.084999999999</v>
+      <c r="B10" s="5">
+        <v>-94035.228000000003</v>
       </c>
       <c r="C10" s="4">
-        <v>-17604.787</v>
+        <v>-56812.387000000002</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="4">
-        <v>-20850.065999999999</v>
+      <c r="F10" s="5">
+        <v>-94037.062000000005</v>
       </c>
       <c r="G10" s="4">
-        <v>-17590.167000000001</v>
+        <v>-56830.474999999999</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>203</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>-94035.228000000003</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>-56812.387000000002</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>-94037.062000000005</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>-56830.474999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="4">
-        <v>-20893.093000000001</v>
+      <c r="B11" s="5">
+        <v>-93985.48</v>
       </c>
       <c r="C11" s="4">
-        <v>-17639.188999999998</v>
+        <v>-56817.408000000003</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="4">
-        <v>-20869.215</v>
+      <c r="F11" s="5">
+        <v>-93987.313999999998</v>
       </c>
       <c r="G11" s="4">
-        <v>-17603.338</v>
+        <v>-56835.495999999999</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>205</v>
+      </c>
+      <c r="I11">
+        <f>IF(ISERROR(VALUE("-93"&amp;B11)), B11,VALUE("-93"&amp;B11))</f>
+        <v>-93985.48</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>-56817.408000000003</v>
+      </c>
+      <c r="M11">
+        <f>IF(ISERROR(VALUE("-93"&amp;F11)), F11,VALUE("-93"&amp;F11))</f>
+        <v>-93987.313999999998</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>-56835.495999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="4">
-        <v>-20926.052</v>
+        <v>-93935.732999999993</v>
       </c>
       <c r="C12" s="4">
-        <v>-17661.861000000001</v>
+        <v>-56822.43</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="4">
-        <v>-20935.123</v>
+        <v>-93949.804999999993</v>
       </c>
       <c r="G12" s="4">
-        <v>-17648.68</v>
+        <v>-56839.283000000003</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>207</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ref="I12:I25" si="4">IF(ISERROR(VALUE("-93"&amp;B12)), B12,VALUE("-93"&amp;B12))</f>
+        <v>-93935.732999999993</v>
+      </c>
+      <c r="J12">
+        <f t="shared" ref="J12:J25" si="5">IF(ISERROR(VALUE("-56"&amp;C12)), C12,VALUE("-56"&amp;C12))</f>
+        <v>-56822.43</v>
+      </c>
+      <c r="M12">
+        <f t="shared" ref="M12:M25" si="6">IF(ISERROR(VALUE("-93"&amp;F12)), F12,VALUE("-93"&amp;F12))</f>
+        <v>-93949.804999999993</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>-56839.283000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B13" s="4">
-        <v>-20959.010999999999</v>
+        <v>-93885.986000000004</v>
       </c>
       <c r="C13" s="4">
-        <v>-17684.531999999999</v>
+        <v>-56827.451000000001</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="4">
-        <v>-20968.072</v>
+        <v>-93887.82</v>
       </c>
       <c r="G13" s="4">
-        <v>-17671.351999999999</v>
+        <v>-56845.538999999997</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>209</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="4"/>
+        <v>-93885.986000000004</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="5"/>
+        <v>-56827.451000000001</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="6"/>
+        <v>-93887.82</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>-56845.538999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="4">
-        <v>-20991.96</v>
+        <v>-93836.239000000001</v>
       </c>
       <c r="C14" s="4">
-        <v>-17707.203000000001</v>
+        <v>-56832.472999999998</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="4">
-        <v>-21001.030999999999</v>
+        <v>-93838.073000000004</v>
       </c>
       <c r="G14" s="4">
-        <v>-17694.023000000001</v>
+        <v>-56850.559999999998</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>211</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="4"/>
+        <v>-93836.239000000001</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="5"/>
+        <v>-56832.472999999998</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="6"/>
+        <v>-93838.073000000004</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>-56850.559999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="4">
-        <v>-21024.92</v>
+        <v>-93786.491999999998</v>
       </c>
       <c r="C15" s="4">
-        <v>-17729.874</v>
+        <v>-56837.493999999999</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="5">
-        <v>-21033991</v>
+      <c r="F15" s="4">
+        <v>-93803.648000000001</v>
       </c>
       <c r="G15" s="4">
-        <v>-17716.694</v>
+        <v>-56854.035000000003</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>213</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="4"/>
+        <v>-93786.491999999998</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="5"/>
+        <v>-56837.493999999999</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>-93803.648000000001</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>-56854.035000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B16" s="4">
-        <v>-21057.88</v>
+        <v>-93736.744000000006</v>
       </c>
       <c r="C16" s="4">
-        <v>-17752.544999999998</v>
+        <v>-56842.516000000003</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>-21066.940999999999</v>
+        <v>-93744.846999999994</v>
       </c>
       <c r="G16" s="4">
-        <v>-17739.365000000002</v>
+        <v>-56859.970999999998</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>215</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="4"/>
+        <v>-93736.744000000006</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="5"/>
+        <v>-56842.516000000003</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>-93744.846999999994</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>-56859.970999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="4">
-        <v>-21090.83</v>
+        <v>-93688.986999999994</v>
       </c>
       <c r="C17" s="4">
-        <v>-17775.216</v>
+        <v>-56847.336000000003</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="4">
-        <v>-21099.901000000002</v>
+        <v>-93689.726999999999</v>
       </c>
       <c r="G17" s="4">
-        <v>-17762.026000000002</v>
+        <v>-56865.534</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>217</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="4"/>
+        <v>-93688.986999999994</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="5"/>
+        <v>-56847.336000000003</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="6"/>
+        <v>-93689.726999999999</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>-56865.534</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="4">
-        <v>-21123.791000000001</v>
+        <v>-93641.23</v>
       </c>
       <c r="C18" s="4">
-        <v>-17797.886999999999</v>
+        <v>-56852.156999999999</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F18" s="4">
-        <v>-21132.862000000001</v>
+        <v>-93643.063999999998</v>
       </c>
       <c r="G18" s="4">
-        <v>-17784.696</v>
+        <v>-56870.243999999999</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>219</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="4"/>
+        <v>-93641.23</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="5"/>
+        <v>-56852.156999999999</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="6"/>
+        <v>-93643.063999999998</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>-56870.243999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="4" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="4">
-        <v>-21156.751</v>
+        <v>-93591.316000000006</v>
       </c>
       <c r="C19" s="4">
-        <v>-17820.546999999999</v>
+        <v>-56857.195</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="4">
-        <v>-21165.812000000002</v>
+        <v>-93593.154999999999</v>
       </c>
       <c r="G19" s="4">
-        <v>-17807.366999999998</v>
+        <v>-56875.281999999999</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>221</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="4"/>
+        <v>-93591.316000000006</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="5"/>
+        <v>-56857.195</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="6"/>
+        <v>-93593.154999999999</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>-56875.281999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="4">
-        <v>-21189.690999999999</v>
-      </c>
-      <c r="C20" s="4">
-        <v>-17843.248</v>
+      <c r="B20" s="5">
+        <v>-93586.289000000004</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-56807.447999999997</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F20" s="4">
-        <v>-21198.773000000001</v>
+        <v>-93575.066999999995</v>
       </c>
       <c r="G20" s="4">
-        <v>-17830.038</v>
+        <v>-56877.107000000004</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="4"/>
+        <v>-93586.289000000004</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="5"/>
+        <v>-56807.447999999997</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="6"/>
+        <v>-93575.066999999995</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>-56877.107000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="F21" s="4">
+        <v>-93573.228000000003</v>
+      </c>
+      <c r="G21" s="4">
+        <v>-56859.021000000001</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="4"/>
+        <v>-93</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="5"/>
+        <v>-56</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="6"/>
+        <v>-93573.228000000003</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>-56859.021000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="4">
-        <v>-21216.873</v>
-      </c>
-      <c r="G22" s="4">
-        <v>-17834.898000000001</v>
+      <c r="F22" s="5">
+        <v>-93568.201000000001</v>
+      </c>
+      <c r="G22" s="5">
+        <v>-56809.273999999998</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" s="4">
-        <v>-21216.023000000001</v>
-      </c>
-      <c r="G23" s="4">
-        <v>-17844.898000000001</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="4"/>
+        <v>-93</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="5"/>
+        <v>-56</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="6"/>
+        <v>-93568.201000000001</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="3"/>
+        <v>-56809.273999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23">
+        <f t="shared" si="4"/>
+        <v>-93</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="5"/>
+        <v>-56</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="6"/>
+        <v>-93</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="3"/>
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24">
+        <f t="shared" si="4"/>
+        <v>-93</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="5"/>
+        <v>-56</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="6"/>
+        <v>-93</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="3"/>
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="4"/>
+      <c r="I25">
+        <f t="shared" si="4"/>
+        <v>-93</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="5"/>
+        <v>-56</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="6"/>
+        <v>-93</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+    </row>
+    <row r="33" spans="8:12">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="8:12">
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
